--- a/data/output/2025/evaluasi_16.xlsx
+++ b/data/output/2025/evaluasi_16.xlsx
@@ -2196,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,6 +2424,146 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-10.68188571970266</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.31177039861034</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.83026914410382</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.572046614214914</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.599670555385</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,6 +2694,90 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>52.22634569590875</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.812610152289526</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1926539077347811</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,6 +2964,118 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.6356325113475864</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>23.36445527114982</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.068774905858839</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.08273536969427332</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2754,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3514,6 +3850,286 @@
       <c r="F27" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-1.741139410707553</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>30.12542814521386</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.2248250906678713</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-20.60965605853169</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-2.475609001786688</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3528,7 +4144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3728,6 +4344,62 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36.52823741562778</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6880795460090197</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3742,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3998,6 +4670,230 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.724685264403963</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.242701079303543</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.93753625765788</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.483880807630434</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-11.95053922172388</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.199176461986775</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-8.641573342971334</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ilir</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.080332186947681</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4100,6 +4996,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.007148613820092</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3422656315218299</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.357759651152783</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.318406093303188</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4114,7 +5122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4174,6 +5182,230 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.383909777455274</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.704654670409049</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.610840055599767</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.047583262677673</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.700572006773037</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.864929497289321</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.071136013089247</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2049183373298381</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4188,7 +5420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4276,6 +5508,202 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.947713185559011</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.5804888715775</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-15.54080496777086</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-7.550000000000001</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.158375899651934</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.984537760580696</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Lahat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3976932178791481</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4290,7 +5718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4658,6 +6086,118 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>22.1140787244559</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.031636999433449</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.976905305783501</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.0895977919313057</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4672,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4984,6 +6524,118 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Palembang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-12.73728562051402</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Palembang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>9.925045135070691</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Palembang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.382412282480317</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Palembang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8.470302085278183</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4998,7 +6650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5142,6 +6794,174 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.16694735800377</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.061108559672109</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>51.90797223893138</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.04351360142651872</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.731155267721997</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Empat Lawang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.961921625870068</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5156,7 +6976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5272,6 +7092,146 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.403958391988129</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.139999999999988</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.66864178883782</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-17.06451175637689</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Muara Enim</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-12.31609779968472</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5286,7 +7246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5374,6 +7334,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.814327380032341</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.702925678992062</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.128179923187025</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyu Asin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2088312176674146</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5388,7 +7460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5448,6 +7520,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3070462179676435</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.730657815875578</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01516934230076952</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5462,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5886,6 +8042,174 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>32.51862772168571</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7.069794697229023</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>35.64545157695756</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.634694255758313</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>24.49895752169204</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.258648051795655</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5900,7 +8224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6047,6 +8371,510 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-6.304203613213636</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.576855913954188</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-13.10649433139382</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>46.70443604185518</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>28.04430437113031</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5859608548599364</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5608605812086851</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5682996904840178</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>26.48453891791791</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.076552232514049</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6.873655696443856</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.711241476611207</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.57802681792035</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-20.56695760005612</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9.955762765652263</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15.79526065268283</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-19.96448134174403</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-4.802139600522283</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
